--- a/files/港岛-半山区东部-Central Peak II.xlsx
+++ b/files/港岛-半山区东部-Central Peak II.xlsx
@@ -609,7 +609,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-09</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-14</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1799,7 +1799,7 @@
         <is>
           <t>Altus Link 洋房6
 4016呎 (4+房)
-(已售)
+(23年-04月)
 $4.10亿
 $102,000/呎</t>
         </is>
@@ -1833,7 +1833,7 @@
         <is>
           <t>Bliss Link 洋房1
 3723呎 (4+房)
-(已售)
+(22年-01月)
 $3.87亿
 $103,895/呎</t>
         </is>
@@ -1842,7 +1842,7 @@
         <is>
           <t>Bliss Link 洋房2
 3695呎 (4+房)
-(已售)
+(21年-11月)
 $3.52亿
 $95,399/呎</t>
         </is>

--- a/files/港岛-半山区东部-Central Peak II.xlsx
+++ b/files/港岛-半山区东部-Central Peak II.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,6 +98,22 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -223,13 +239,13 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -610,7 +626,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-半山区东部-Central Peak II.xlsx
+++ b/files/港岛-半山区东部-Central Peak II.xlsx
@@ -626,7 +626,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-半山区东部-Central Peak II.xlsx
+++ b/files/港岛-半山区东部-Central Peak II.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -629,6 +629,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -686,6 +690,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -736,6 +760,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -786,6 +830,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -836,6 +900,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -886,6 +970,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -932,6 +1036,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -982,6 +1106,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1032,6 +1176,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1078,6 +1242,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1124,6 +1308,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1174,6 +1378,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1224,6 +1448,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1274,6 +1518,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1324,6 +1588,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1374,6 +1658,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1424,6 +1728,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1474,6 +1798,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1524,6 +1868,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1574,6 +1938,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1624,13 +2008,33 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1815,7 +2219,7 @@
         <is>
           <t>Altus Link 洋房6
 4016呎 (4+房)
-(23年-04月)
+(23年-04月-26日)
 $4.10亿
 $102,000/呎</t>
         </is>
@@ -1849,7 +2253,7 @@
         <is>
           <t>Bliss Link 洋房1
 3723呎 (4+房)
-(22年-01月)
+(22年-01月-09日)
 $3.87亿
 $103,895/呎</t>
         </is>
@@ -1858,7 +2262,7 @@
         <is>
           <t>Bliss Link 洋房2
 3695呎 (4+房)
-(21年-11月)
+(21年-11月-14日)
 $3.52亿
 $95,399/呎</t>
         </is>

--- a/files/港岛-半山区东部-Central Peak II.xlsx
+++ b/files/港岛-半山区东部-Central Peak II.xlsx
@@ -242,13 +242,13 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -787,7 +787,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Altus Link 洋房2</t>
+          <t>Altus Link 洋房3</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>3648</v>
+        <v>3686</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Altus Link 洋房3</t>
+          <t>Altus Link 洋房5</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3686</v>
+        <v>4022</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Altus Link 洋房5</t>
+          <t>Altus Link 洋房6</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -946,27 +946,23 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4022</v>
+        <v>4016</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2023-04-26</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>409632000</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>102000</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -997,7 +993,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Altus Link 洋房6</t>
+          <t>Altus Link 洋房7</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1016,23 +1012,27 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4016</v>
+        <v>3671</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>409632000</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>102000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Altus Link 洋房7</t>
+          <t>Altus Link 洋房8</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3671</v>
+        <v>3954</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Altus Link 洋房8</t>
+          <t>Bliss Link 洋房1</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1152,27 +1152,23 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3954</v>
+        <v>3723</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2022-01-09</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>386800000</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>103895</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1203,7 +1199,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房1</t>
+          <t>Bliss Link 洋房2</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1222,7 +1218,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3723</v>
+        <v>3695</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1231,14 +1227,14 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2022-01-09</t>
+          <t>2021-11-14</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>386800000</v>
+        <v>352500000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>103895</v>
+        <v>95399</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1269,7 +1265,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房2</t>
+          <t>Bliss Link 洋房3</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1288,23 +1284,27 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3695</v>
+        <v>3688</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>352500000</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>95399</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房3</t>
+          <t>Bliss Link 洋房6</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1354,11 +1354,11 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3688</v>
+        <v>3691</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1398,14 +1398,14 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房6</t>
+          <t>Bliss Link 洋房7</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3691</v>
+        <v>3686</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房7</t>
+          <t>Bliss Link 洋房8</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3686</v>
+        <v>3714</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房8</t>
+          <t>Colmo Link 洋房1</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1560,11 +1560,11 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3714</v>
+        <v>2776</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房1</t>
+          <t>Colmo Link 洋房2</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2776</v>
+        <v>2754</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房2</t>
+          <t>Colmo Link 洋房3</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房3</t>
+          <t>Colmo Link 洋房6</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1825,7 +1825,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房6</t>
+          <t>Colmo Link 洋房7</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1895,7 +1895,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房7</t>
+          <t>Colmo Link 洋房8</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1914,7 +1914,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2754</v>
+        <v>2780</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1957,76 +1957,6 @@
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Colmo Link 洋房8</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>2780</v>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2102,7 +2032,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>19 套</t>
+          <t>18 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -2127,7 +2057,7 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>15 套</t>
+          <t>14 套</t>
         </is>
       </c>
     </row>
@@ -2188,15 +2118,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>Altus Link 洋房2
-3648呎 (4+房)
-(待售)
-暂无价格
-暂无呎价</t>
-        </is>
-      </c>
+      <c r="C6" s="17" t="inlineStr"/>
       <c r="D6" s="16" t="inlineStr">
         <is>
           <t>Altus Link 洋房3
@@ -2215,7 +2137,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
         <is>
           <t>Altus Link 洋房6
 4016呎 (4+房)
@@ -2249,7 +2171,7 @@
           <t>Bliss Link</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Bliss Link 洋房1
 3723呎 (4+房)
@@ -2258,7 +2180,7 @@
 $103,895/呎</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>Bliss Link 洋房2
 3695呎 (4+房)
@@ -2267,7 +2189,7 @@
 $95,399/呎</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Bliss Link 洋房3
 3688呎 (4+房)
@@ -2276,7 +2198,7 @@
 -</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr"/>
+      <c r="E7" s="17" t="inlineStr"/>
       <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Bliss Link 洋房6
@@ -2338,7 +2260,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr"/>
+      <c r="E8" s="17" t="inlineStr"/>
       <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Colmo Link 洋房6

--- a/files/港岛-半山区东部-Central Peak II.xlsx
+++ b/files/港岛-半山区东部-Central Peak II.xlsx
@@ -242,10 +242,10 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -787,7 +787,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Altus Link 洋房3</t>
+          <t>Altus Link 洋房2</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>3686</v>
+        <v>3648</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Altus Link 洋房5</t>
+          <t>Altus Link 洋房3</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>4022</v>
+        <v>3686</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Altus Link 洋房6</t>
+          <t>Altus Link 洋房5</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -946,23 +946,27 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4016</v>
+        <v>4022</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>409632000</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>102000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -993,7 +997,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Altus Link 洋房7</t>
+          <t>Altus Link 洋房6</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1012,27 +1016,23 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3671</v>
+        <v>4016</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2023-04-26</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>409632000</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>102000</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Altus Link 洋房8</t>
+          <t>Altus Link 洋房7</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3954</v>
+        <v>3671</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房1</t>
+          <t>Altus Link 洋房8</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1152,23 +1152,27 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3723</v>
+        <v>3954</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2022-01-09</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>386800000</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>103895</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1199,7 +1203,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房2</t>
+          <t>Bliss Link 洋房1</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1218,7 +1222,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3695</v>
+        <v>3723</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1227,14 +1231,14 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
+          <t>2022-01-09</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>352500000</v>
+        <v>386800000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>95399</v>
+        <v>103895</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -2047,7 +2051,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>3 套</t>
+          <t>2 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -2057,7 +2061,7 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>14 套</t>
+          <t>15 套</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2122,15 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr"/>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Altus Link 洋房2
+3648呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
           <t>Altus Link 洋房3
@@ -2137,11 +2149,11 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>Altus Link 洋房6
 4016呎 (4+房)
-(23年-04月-26日)
+(23年-04月)
 $4.10亿
 $102,000/呎</t>
         </is>
@@ -2171,24 +2183,16 @@
           <t>Bliss Link</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Bliss Link 洋房1
 3723呎 (4+房)
-(22年-01月-09日)
+(22年-01月)
 $3.87亿
 $103,895/呎</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>Bliss Link 洋房2
-3695呎 (4+房)
-(21年-11月-14日)
-$3.52亿
-$95,399/呎</t>
-        </is>
-      </c>
+      <c r="C7" s="18" t="inlineStr"/>
       <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Bliss Link 洋房3
@@ -2198,7 +2202,7 @@
 -</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr"/>
       <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Bliss Link 洋房6
@@ -2260,7 +2264,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
       <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Colmo Link 洋房6

--- a/files/港岛-半山区东部-Central Peak II.xlsx
+++ b/files/港岛-半山区东部-Central Peak II.xlsx
@@ -245,10 +245,10 @@
     <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1269,7 +1269,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房3</t>
+          <t>Bliss Link 洋房2</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1288,27 +1288,23 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3688</v>
+        <v>3695</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2021-11-14</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>352500000</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>95399</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1317,12 +1313,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1332,14 +1328,14 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房6</t>
+          <t>Bliss Link 洋房3</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1358,11 +1354,11 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3691</v>
+        <v>3688</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1372,12 +1368,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1387,12 +1383,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1402,14 +1398,14 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房7</t>
+          <t>Bliss Link 洋房6</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1428,7 +1424,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3686</v>
+        <v>3691</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1479,7 +1475,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Bliss Link 洋房8</t>
+          <t>Bliss Link 洋房7</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1498,7 +1494,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3714</v>
+        <v>3686</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1549,7 +1545,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房1</t>
+          <t>Bliss Link 洋房8</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1564,11 +1560,11 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2776</v>
+        <v>3714</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1619,7 +1615,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房2</t>
+          <t>Colmo Link 洋房1</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1638,7 +1634,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2754</v>
+        <v>2776</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1689,7 +1685,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房3</t>
+          <t>Colmo Link 洋房2</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1759,7 +1755,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房6</t>
+          <t>Colmo Link 洋房3</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1829,7 +1825,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Colmo Link 洋房7</t>
+          <t>Colmo Link 洋房6</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1899,68 +1895,138 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>Colmo Link 洋房7</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>2754</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
           <t>Colmo Link 洋房8</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>3房</t>
         </is>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E21" s="4" t="n">
         <v>2780</v>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>待售</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2036,7 +2102,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>18 套</t>
+          <t>19 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -2051,7 +2117,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>2 套</t>
+          <t>3 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -2153,7 +2219,7 @@
         <is>
           <t>Altus Link 洋房6
 4016呎 (4+房)
-(23年-04月)
+(23年-04月-26日)
 $4.10亿
 $102,000/呎</t>
         </is>
@@ -2187,13 +2253,21 @@
         <is>
           <t>Bliss Link 洋房1
 3723呎 (4+房)
-(22年-01月)
+(22年-01月-09日)
 $3.87亿
 $103,895/呎</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr"/>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Bliss Link 洋房2
+3695呎 (4+房)
+(21年-11月-14日)
+$3.52亿
+$95,399/呎</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>Bliss Link 洋房3
 3688呎 (4+房)
@@ -2202,7 +2276,7 @@
 -</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr"/>
+      <c r="E7" s="19" t="inlineStr"/>
       <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Bliss Link 洋房6
@@ -2264,7 +2338,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr"/>
+      <c r="E8" s="19" t="inlineStr"/>
       <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Colmo Link 洋房6
